--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1397,6 +1397,217 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131304007</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57881</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>329500</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6454312</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131303966</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97880</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>329440</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6454315</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ann-Charlotte Svensson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -1507,7 +1507,7 @@
         <v>131303966</v>
       </c>
       <c r="B10" t="n">
-        <v>97880</v>
+        <v>97883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -1507,7 +1507,7 @@
         <v>131303966</v>
       </c>
       <c r="B10" t="n">
-        <v>97883</v>
+        <v>97884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -1402,7 +1402,7 @@
         <v>131304007</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>131303966</v>
       </c>
       <c r="B10" t="n">
-        <v>97884</v>
+        <v>97886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -1402,7 +1402,7 @@
         <v>131304007</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>131303966</v>
       </c>
       <c r="B10" t="n">
-        <v>97886</v>
+        <v>97887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -1402,7 +1402,7 @@
         <v>131304007</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>131303966</v>
       </c>
       <c r="B10" t="n">
-        <v>97887</v>
+        <v>97888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -1402,7 +1402,7 @@
         <v>131304007</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>131303966</v>
       </c>
       <c r="B10" t="n">
-        <v>97888</v>
+        <v>97891</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -1402,7 +1402,7 @@
         <v>131304007</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>131303966</v>
       </c>
       <c r="B10" t="n">
-        <v>97891</v>
+        <v>97892</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115053794</v>
+        <v>115053812</v>
       </c>
       <c r="B2" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>329318</v>
+        <v>329274</v>
       </c>
       <c r="R2" t="n">
-        <v>6454435</v>
+        <v>6454441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115053830</v>
+        <v>115053826</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,7 +807,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>329207</v>
+        <v>329197</v>
       </c>
       <c r="R3" t="n">
         <v>6454498</v>
@@ -853,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115053826</v>
+        <v>115053856</v>
       </c>
       <c r="B4" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2606</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>329197</v>
+        <v>329561</v>
       </c>
       <c r="R4" t="n">
-        <v>6454498</v>
+        <v>6454320</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115053796</v>
+        <v>115053792</v>
       </c>
       <c r="B5" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>329213</v>
+        <v>329572</v>
       </c>
       <c r="R5" t="n">
-        <v>6454496</v>
+        <v>6454344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115053795</v>
+        <v>115053794</v>
       </c>
       <c r="B6" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1128,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>329273</v>
+        <v>329318</v>
       </c>
       <c r="R6" t="n">
-        <v>6454475</v>
+        <v>6454435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115053845</v>
+        <v>115053795</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>329284</v>
+        <v>329273</v>
       </c>
       <c r="R7" t="n">
-        <v>6454470</v>
+        <v>6454475</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-03-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115053812</v>
+        <v>115053796</v>
       </c>
       <c r="B8" t="n">
-        <v>95923</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>329274</v>
+        <v>329213</v>
       </c>
       <c r="R8" t="n">
-        <v>6454441</v>
+        <v>6454496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131304007</v>
+        <v>115053830</v>
       </c>
       <c r="B9" t="n">
-        <v>57901</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1428,27 +1383,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sollum, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>329500</v>
+        <v>329207</v>
       </c>
       <c r="R9" t="n">
-        <v>6454312</v>
+        <v>6454498</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1472,12 +1419,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1492,22 +1444,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131303966</v>
+        <v>115053837</v>
       </c>
       <c r="B10" t="n">
-        <v>97909</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1515,45 +1467,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sollum, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>329440</v>
+        <v>329350</v>
       </c>
       <c r="R10" t="n">
-        <v>6454315</v>
+        <v>6454368</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,12 +1521,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2024-03-06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gamla hack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,22 +1540,538 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ann-Charlotte Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>115053843</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>329544</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6454296</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>115053844</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>329458</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6454241</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>115053845</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>329284</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6454470</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-03-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska hack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131304007</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>329500</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6454312</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131303966</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sollum, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>329440</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6454315</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anna Svensson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4017-2026 artfynd.xlsx
+++ b/artfynd/A 4017-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053812</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053826</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053856</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053794</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053795</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053796</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053830</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053837</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053843</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053844</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115053845</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1966,6 +2031,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131304007</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2072,8 +2142,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131303966</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>